--- a/Merise/dictionnaire des données cas video.xlsx
+++ b/Merise/dictionnaire des données cas video.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\CDA\Merise\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DF9A177-4308-45B0-9375-0C1E25CC8FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{659200B2-34AF-4C33-86DD-F3169B4925CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7DEBD8F6-EA5A-4868-A2AB-86E6B61B2148}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="193">
   <si>
     <t>Code</t>
   </si>
@@ -219,12 +219,6 @@
     <t>identifiant/code client/numero adherent</t>
   </si>
   <si>
-    <t>nbr locatio en cours</t>
-  </si>
-  <si>
-    <t>montant total gagné</t>
-  </si>
-  <si>
     <t>Entité</t>
   </si>
   <si>
@@ -393,9 +387,6 @@
     <t xml:space="preserve"> vaccinationEffectue</t>
   </si>
   <si>
-    <t>veterinaire date avcciantion</t>
-  </si>
-  <si>
     <t>idCourses</t>
   </si>
   <si>
@@ -462,18 +453,6 @@
     <t>prenomJockey</t>
   </si>
   <si>
-    <t>numeroAdresseJockey</t>
-  </si>
-  <si>
-    <t>rueAdresseJockey</t>
-  </si>
-  <si>
-    <t>codePostalAdresseJockey</t>
-  </si>
-  <si>
-    <t>villeAdresseJockey</t>
-  </si>
-  <si>
     <t>nbrCourseJockey</t>
   </si>
   <si>
@@ -489,18 +468,6 @@
     <t>prenom du jockey</t>
   </si>
   <si>
-    <t>numero d'adresse du jockey</t>
-  </si>
-  <si>
-    <t>rue de l'adresse du jockey</t>
-  </si>
-  <si>
-    <t>code postal du jockey</t>
-  </si>
-  <si>
-    <t>ville du jockey</t>
-  </si>
-  <si>
     <t>identifiant du cheval</t>
   </si>
   <si>
@@ -567,9 +534,6 @@
     <t>lieu du course</t>
   </si>
   <si>
-    <t>id du partant</t>
-  </si>
-  <si>
     <t>place du corde</t>
   </si>
   <si>
@@ -585,9 +549,6 @@
     <t>nbr du cheval</t>
   </si>
   <si>
-    <t>id du jockey</t>
-  </si>
-  <si>
     <t>heure</t>
   </si>
   <si>
@@ -604,13 +565,61 @@
   </si>
   <si>
     <t>trot,galop,obstable , non nulle</t>
+  </si>
+  <si>
+    <t>Cas Horse</t>
+  </si>
+  <si>
+    <t>Cas Video</t>
+  </si>
+  <si>
+    <t>cheval</t>
+  </si>
+  <si>
+    <t>proprietaire</t>
+  </si>
+  <si>
+    <t>veterinaire</t>
+  </si>
+  <si>
+    <t>partant</t>
+  </si>
+  <si>
+    <t>jockey</t>
+  </si>
+  <si>
+    <t>course</t>
+  </si>
+  <si>
+    <t>identifiant du partant</t>
+  </si>
+  <si>
+    <t>identifiant du jockey</t>
+  </si>
+  <si>
+    <t>nomCheval,dateNaissance,nomMere,nomPère,race,sexe,lieuNaissance,couleur</t>
+  </si>
+  <si>
+    <t>vaccinationEffectue</t>
+  </si>
+  <si>
+    <t>nbrPartant,dateCourse,distance,prixGagnant,heureDepart,nomEpreuve,typeCourse,lieuCourse</t>
+  </si>
+  <si>
+    <t>nomJockey,placeCorde,handicap,gains,couleurProprio,nbrCourseCheval</t>
+  </si>
+  <si>
+    <t>nomJockey,prenomJockey,nbrCourseJockey</t>
+  </si>
+  <si>
+    <t>nomProprio,prenomProprio,numeroAdresseProprio,rueAdresseProprio,codePostalAdresseProprio,villeAdresseProprio,nbrCheval,typeProprio</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -618,8 +627,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -630,12 +647,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor theme="0" tint="-0.14999847407452621"/>
       </patternFill>
     </fill>
   </fills>
@@ -651,7 +662,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -662,13 +673,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -696,8 +702,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2B1A97C4-5954-4402-A45D-33CE9EF78804}" name="Tableau1" displayName="Tableau1" ref="B2:F29" totalsRowShown="0" headerRowDxfId="1">
-  <autoFilter ref="B2:F29" xr:uid="{2B1A97C4-5954-4402-A45D-33CE9EF78804}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2B1A97C4-5954-4402-A45D-33CE9EF78804}" name="Tableau1" displayName="Tableau1" ref="B3:F26" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="B3:F26" xr:uid="{2B1A97C4-5954-4402-A45D-33CE9EF78804}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{2DBBE63F-A630-4324-8144-45D649B7F616}" name="Code"/>
     <tableColumn id="2" xr3:uid="{4D0B872D-E243-4AC4-8543-E078329423EE}" name="Description"/>
@@ -710,27 +716,40 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{54A361AF-8B44-449C-A59F-9A84DDF6DEF2}" name="Tableau24" displayName="Tableau24" ref="C41:F46" totalsRowShown="0">
-  <autoFilter ref="C41:F46" xr:uid="{54A361AF-8B44-449C-A59F-9A84DDF6DEF2}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{54A361AF-8B44-449C-A59F-9A84DDF6DEF2}" name="Tableau24" displayName="Tableau24" ref="C33:F38" totalsRowShown="0">
+  <autoFilter ref="C33:F38" xr:uid="{54A361AF-8B44-449C-A59F-9A84DDF6DEF2}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{C230FCC0-3BB8-47B6-A053-63B28EEF5ED1}" name="Description"/>
     <tableColumn id="2" xr3:uid="{9127BB2C-3EA5-4E54-AF5D-EF0E639369DE}" name="Entité"/>
     <tableColumn id="3" xr3:uid="{DFF41EE3-D3DF-4551-8CEC-F58353448372}" name="Identifiant"/>
     <tableColumn id="4" xr3:uid="{5972F651-7121-4F31-BECD-2DC61D6C0546}" name="Composants"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium19" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium20" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AF4274DC-6660-4091-8730-C3700817E3FA}" name="Tableau2" displayName="Tableau2" ref="B52:F100" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="B52:F100" xr:uid="{AF4274DC-6660-4091-8730-C3700817E3FA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AF4274DC-6660-4091-8730-C3700817E3FA}" name="Tableau2" displayName="Tableau2" ref="B47:F95" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="B47:F95" xr:uid="{AF4274DC-6660-4091-8730-C3700817E3FA}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{5EA16605-98EB-47C7-AAEF-67905F84C7D2}" name="Code"/>
     <tableColumn id="2" xr3:uid="{B2588F03-ADA2-4C14-9D71-27E418521286}" name="Description"/>
     <tableColumn id="3" xr3:uid="{152AECC6-CE9C-41E8-963F-E39DE988F28E}" name="Type"/>
     <tableColumn id="4" xr3:uid="{9AD0350C-93C9-4BAF-8F4C-DE33C20CCCBE}" name="Taille"/>
     <tableColumn id="5" xr3:uid="{40CD1E1D-02E4-42A0-A39A-15DE89395B9B}" name="Contraintes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B9A14E71-4EEE-480E-9E88-49AD83D8135A}" name="Tableau4" displayName="Tableau4" ref="C100:F106" totalsRowShown="0">
+  <autoFilter ref="C100:F106" xr:uid="{B9A14E71-4EEE-480E-9E88-49AD83D8135A}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{0BF42B88-489E-4211-9D27-82CE1CF50725}" name="Description"/>
+    <tableColumn id="2" xr3:uid="{AD6BCD25-EE15-4808-8713-F0D3D9766171}" name="Entité"/>
+    <tableColumn id="3" xr3:uid="{55F762DA-2D47-41D1-AED4-DDE4DB5F8ACA}" name="Identifiant"/>
+    <tableColumn id="4" xr3:uid="{DA4AD7CD-560D-4BF0-886D-4B6A06821030}" name="Composants"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium21" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1033,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD44A88-082C-4555-9EAF-88A937B6897B}">
-  <dimension ref="B2:F109"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="29.140625" customWidth="1"/>
@@ -1043,214 +1062,202 @@
     <col min="6" max="6" width="124.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="2">
+      <c r="D4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="2">
         <v>4</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="D5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="2">
         <v>30</v>
       </c>
-      <c r="F4" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+      <c r="F5" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="D6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="2">
         <v>20</v>
       </c>
-      <c r="F5" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
+      <c r="F6" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="D7" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="2">
         <v>4</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
+      <c r="F7" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="D8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="2">
         <v>30</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+      <c r="F8" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="D9" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="2">
         <v>5</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+      <c r="F9" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E9" s="2">
+      <c r="D10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="2">
         <v>25</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+      <c r="F10" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E10" s="2">
+      <c r="D11" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="2">
         <v>10</v>
       </c>
-      <c r="F10" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+      <c r="F11" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" s="2">
+      <c r="D12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="2">
         <v>20</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="3" t="s">
+      <c r="F12" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C14" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="2">
-        <v>8</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>19</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>30</v>
@@ -1259,117 +1266,117 @@
         <v>8</v>
       </c>
       <c r="F14" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="2">
+        <v>8</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C16" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E16" s="2">
         <v>4</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
+      <c r="F16" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" s="2">
+      <c r="D17" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="2">
         <v>6</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" s="2">
-        <v>20</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2">
-        <v>4</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>53</v>
+        <v>20</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" s="2">
+        <v>4</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C20" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="2">
+      <c r="D20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="2">
         <v>2</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="3" t="s">
+      <c r="F20" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C21" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="2">
-        <v>30</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>31</v>
@@ -1377,302 +1384,393 @@
       <c r="E21" s="2">
         <v>30</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>57</v>
+      <c r="F21" s="2" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22" s="2">
+        <v>30</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C23" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="2">
+      <c r="D23" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23" s="2">
         <v>20</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
+      <c r="F23" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C24" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E23" s="2">
+      <c r="D24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24" s="2">
         <v>3</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="F24" s="2" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24" s="2">
-        <v>20</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E25" s="2">
+        <v>20</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C26" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" s="2">
+      <c r="D26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="2">
         <v>7</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C33" t="s">
+        <v>1</v>
+      </c>
+      <c r="D33" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" t="s">
+        <v>62</v>
+      </c>
+      <c r="F33" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C34" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F34" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C35" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F36" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C37" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F37" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C38" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="5"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="5"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="5"/>
+    </row>
+    <row r="45" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A45" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B47" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B48" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E48" s="2">
+        <v>30</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A49" s="4"/>
+      <c r="B49" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" s="2">
+        <v>30</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
-    </row>
-    <row r="41" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C41" t="s">
-        <v>1</v>
-      </c>
-      <c r="D41" t="s">
-        <v>63</v>
-      </c>
-      <c r="E41" t="s">
-        <v>64</v>
-      </c>
-      <c r="F41" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C42" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F42" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C43" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F43" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="44" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C44" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F44" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="45" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C45" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F45" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="46" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C46" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F46" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B52" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>3</v>
+      <c r="C50" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E50" s="2">
+        <v>8</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B51" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" s="2">
+        <v>30</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B52" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52" s="2">
+        <v>30</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B53" s="3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B53" s="2" t="s">
         <v>78</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="E53" s="2">
         <v>30</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B54" s="4" t="s">
-        <v>131</v>
+      <c r="F53" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="E54" s="2">
-        <v>30</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+        <v>7</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B55" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E55" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="2" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E56" s="2">
-        <v>30</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B57" s="2" t="s">
-        <v>133</v>
+        <v>15</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B57" s="3" t="s">
+        <v>82</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="E57" s="2">
         <v>30</v>
       </c>
-      <c r="F57" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F57" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="2" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>162</v>
+        <v>97</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>31</v>
@@ -1680,107 +1778,107 @@
       <c r="E58" s="2">
         <v>30</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="F58" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="2" t="s">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>163</v>
+        <v>98</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="E59" s="2">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B60" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>164</v>
+        <v>84</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="E60" s="2">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B61" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>165</v>
+        <v>85</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E61" s="2">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B62" s="3" t="s">
-        <v>84</v>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B62" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E62" s="2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B63" s="2" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E63" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B64" s="2" t="s">
-        <v>97</v>
+        <v>136</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>100</v>
+        <v>155</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="E64" s="2">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>57</v>
@@ -1788,50 +1886,50 @@
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B65" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="E65" s="2">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>57</v>
+        <v>94</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B66" s="2" t="s">
-        <v>92</v>
+      <c r="B66" s="3" t="s">
+        <v>99</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>87</v>
+        <v>156</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="E66" s="2">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B67" s="2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="E67" s="2">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>57</v>
@@ -1839,16 +1937,16 @@
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B68" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E68" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>57</v>
@@ -1856,16 +1954,16 @@
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B69" s="2" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="E69" s="2">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>57</v>
@@ -1873,50 +1971,50 @@
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B70" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="E70" s="2">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>96</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B71" s="3" t="s">
-        <v>101</v>
+      <c r="B71" s="2" t="s">
+        <v>106</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>167</v>
+        <v>110</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E71" s="2">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B72" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E72" s="2">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>57</v>
@@ -1924,81 +2022,81 @@
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B73" s="2" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="E73" s="2">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>57</v>
+        <v>114</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B74" s="2" t="s">
-        <v>106</v>
+      <c r="B74" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>110</v>
+        <v>146</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E74" s="2">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B75" s="2" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>111</v>
+        <v>157</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E75" s="2">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B76" s="2" t="s">
-        <v>108</v>
+      <c r="B76" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>112</v>
+        <v>158</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E76" s="2">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B77" s="2" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>113</v>
+        <v>159</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="E77" s="2">
         <v>25</v>
@@ -2009,84 +2107,84 @@
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B78" s="2" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>115</v>
+        <v>174</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="E78" s="2">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>116</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B79" s="3" t="s">
-        <v>117</v>
+      <c r="B79" s="2" t="s">
+        <v>119</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>76</v>
+        <v>32</v>
       </c>
       <c r="E79" s="2">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B80" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>31</v>
+        <v>173</v>
       </c>
       <c r="E80" s="2">
-        <v>20</v>
+        <v>10000</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B81" s="3" t="s">
-        <v>120</v>
+      <c r="B81" s="2" t="s">
+        <v>121</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>76</v>
+        <v>171</v>
       </c>
       <c r="E81" s="2">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B82" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="E82" s="2">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>57</v>
@@ -2094,67 +2192,67 @@
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="E83" s="2">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>52</v>
+        <v>176</v>
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B84" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E84" s="2">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B85" s="2" t="s">
-        <v>123</v>
+      <c r="B85" s="3" t="s">
+        <v>127</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>186</v>
+        <v>74</v>
       </c>
       <c r="E85" s="2">
-        <v>10000</v>
+        <v>30</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B86" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="E86" s="2">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>57</v>
@@ -2162,10 +2260,10 @@
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B87" s="2" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>31</v>
@@ -2179,116 +2277,114 @@
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B88" s="2" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>129</v>
+        <v>31</v>
       </c>
       <c r="E88" s="2">
-        <v>15</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>189</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="F88" s="2"/>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B89" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E89" s="2">
-        <v>20</v>
+        <v>10000</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B90" s="3" t="s">
-        <v>130</v>
+      <c r="B90" s="2" t="s">
+        <v>135</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="E90" s="2">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B91" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>148</v>
+        <v>170</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="E91" s="2">
+        <v>10</v>
+      </c>
+      <c r="F91" s="2"/>
+    </row>
+    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B92" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E92" s="2">
         <v>30</v>
       </c>
-      <c r="F91" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="92" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B92" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E92" s="2">
-        <v>20</v>
-      </c>
       <c r="F92" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B93" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>179</v>
+        <v>141</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E93" s="2">
-        <v>20</v>
-      </c>
-      <c r="F93" s="2"/>
+        <v>30</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B94" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>180</v>
+        <v>143</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E94" s="2">
-        <v>10000</v>
+        <v>20</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>57</v>
@@ -2296,183 +2392,127 @@
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B95" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C95" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E95" s="2">
+        <v>10</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="100" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C100" t="s">
+        <v>1</v>
+      </c>
+      <c r="D100" t="s">
+        <v>61</v>
+      </c>
+      <c r="E100" t="s">
+        <v>62</v>
+      </c>
+      <c r="F100" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="101" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C101" t="s">
+        <v>144</v>
+      </c>
+      <c r="D101" t="s">
+        <v>179</v>
+      </c>
+      <c r="E101" t="s">
+        <v>76</v>
+      </c>
+      <c r="F101" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="102" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C102" t="s">
+        <v>145</v>
+      </c>
+      <c r="D102" t="s">
+        <v>180</v>
+      </c>
+      <c r="E102" t="s">
+        <v>82</v>
+      </c>
+      <c r="F102" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="103" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C103" t="s">
+        <v>146</v>
+      </c>
+      <c r="D103" t="s">
         <v>181</v>
       </c>
-      <c r="D95" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E95" s="2">
-        <v>15</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="96" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B96" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="E103" t="s">
+        <v>115</v>
+      </c>
+      <c r="F103" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="104" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C104" t="s">
+        <v>158</v>
+      </c>
+      <c r="D104" t="s">
+        <v>184</v>
+      </c>
+      <c r="E104" t="s">
+        <v>117</v>
+      </c>
+      <c r="F104" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="105" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C105" t="s">
+        <v>185</v>
+      </c>
+      <c r="D105" t="s">
         <v>182</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E96" s="2">
-        <v>10</v>
-      </c>
-      <c r="F96" s="2"/>
-    </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B97" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C97" s="2" t="s">
+      <c r="E105" t="s">
+        <v>127</v>
+      </c>
+      <c r="F105" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="106" spans="3:6" x14ac:dyDescent="0.25">
+      <c r="C106" t="s">
+        <v>186</v>
+      </c>
+      <c r="D106" t="s">
         <v>183</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E97" s="2">
-        <v>30</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B98" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E98" s="2">
-        <v>30</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B99" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E99" s="2">
-        <v>20</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B100" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E100" s="2">
-        <v>10</v>
-      </c>
-      <c r="F100" s="2" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B104" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="106" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B106" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="D106" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E106" s="5">
-        <v>4</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B107" s="6" t="s">
-        <v>143</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E107" s="6">
-        <v>30</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B108" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E108" s="5">
-        <v>5</v>
-      </c>
-      <c r="F108" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B109" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E109" s="6">
-        <v>25</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>57</v>
+      <c r="E106" t="s">
+        <v>137</v>
+      </c>
+      <c r="F106" t="s">
+        <v>191</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="3">
-    <tablePart r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="4">
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>